--- a/datasets/pco/02 Maestro de cargos sintético.xlsx
+++ b/datasets/pco/02 Maestro de cargos sintético.xlsx
@@ -1413,7 +1413,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DATOS 100 % FICTICIOS para el programa IA-abilities (Coknow). No corresponden a la Compañía ni a ninguna persona real.</t>
+          <t>DATOS 100 % FICTICIOS para el programa IA-abilities. No corresponden a la Compañía ni a ninguna persona real.</t>
         </is>
       </c>
     </row>

--- a/datasets/pco/02 Maestro de cargos sintético.xlsx
+++ b/datasets/pco/02 Maestro de cargos sintético.xlsx
@@ -1350,7 +1350,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Vigente</t>
@@ -1376,7 +1375,6 @@
       <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -1420,7 +1418,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maestro de cargos sintético con errores sembrados a propósito (duplicados, banda vacía, nivel que no coincide con la banda, fechas faltantes o de más de 3 años).</t>
+          <t>Maestro de cargos sintético.</t>
         </is>
       </c>
     </row>
